--- a/data/Mapa_de_procesos.xlsx
+++ b/data/Mapa_de_procesos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/SIGEI/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Ficha-de-indicadores/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="6" documentId="8_{4F3D0CF1-B82B-466E-8E1D-F6400865F98A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1214C92-FCFE-4C85-8394-873D6FBD2D70}"/>
@@ -1103,7 +1103,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>22</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>17</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>85</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>40</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>22</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>40</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>17</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>40</v>
       </c>
@@ -2065,7 +2065,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>17</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>40</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
         <v>40</v>
       </c>
